--- a/analysis/tables/gpt-neo-125m.xlsx
+++ b/analysis/tables/gpt-neo-125m.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4653191314089975</v>
+        <v>0.3381319021572047</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.09111809708896604</v>
+        <v>-0.04148405640533964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.465x - 0.091</t>
+          <t>y = 0.338x - 0.041</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5310264851532205</v>
+        <v>0.53102648515322</v>
       </c>
       <c r="H3" t="n">
         <v>0.07106507919241614</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1958185059209972</v>
+        <v>0.1226860173224732</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3742010343200315</v>
+        <v>0.2966478457518651</v>
       </c>
       <c r="K3" t="n">
         <v>0.08024303615612118</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.609132729152529</v>
+        <v>0.3374301215844812</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07307883703361051</v>
+        <v>-0.03800818616088122</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 2.609x + 0.073</t>
+          <t>y = 0.337x - 0.038</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5929073685334815</v>
+        <v>0.5347842749825662</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06999188082721414</v>
+        <v>0.07099990795242518</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02800886141861675</v>
+        <v>0.1126401697110056</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68221156618614</v>
+        <v>0.2994219354236</v>
       </c>
       <c r="K4" t="n">
         <v>0.08024303615612118</v>
